--- a/artfynd/A 44917-2024 artfynd.xlsx
+++ b/artfynd/A 44917-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120835381</v>
+        <v>120835333</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630304</v>
+        <v>630218</v>
       </c>
       <c r="R2" t="n">
-        <v>6972552</v>
+        <v>6972503</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>120835192</v>
       </c>
       <c r="B3" t="n">
-        <v>90698</v>
+        <v>90708</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120835333</v>
+        <v>120835469</v>
       </c>
       <c r="B4" t="n">
-        <v>90687</v>
+        <v>90662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630218</v>
+        <v>630342</v>
       </c>
       <c r="R4" t="n">
-        <v>6972503</v>
+        <v>6972562</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120835469</v>
+        <v>120835381</v>
       </c>
       <c r="B5" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630342</v>
+        <v>630304</v>
       </c>
       <c r="R5" t="n">
-        <v>6972562</v>
+        <v>6972552</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
